--- a/artfynd/A 7583-2026 artfynd.xlsx
+++ b/artfynd/A 7583-2026 artfynd.xlsx
@@ -910,12 +910,7 @@
         <v>122923641</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7583-2026 artfynd.xlsx
+++ b/artfynd/A 7583-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122923641</v>
       </c>
       <c r="B4" t="n">
-        <v>57076</v>
+        <v>57078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7583-2026 artfynd.xlsx
+++ b/artfynd/A 7583-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122923641</v>
       </c>
       <c r="B4" t="n">
-        <v>57078</v>
+        <v>57079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7583-2026 artfynd.xlsx
+++ b/artfynd/A 7583-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122923641</v>
       </c>
       <c r="B4" t="n">
-        <v>57079</v>
+        <v>57082</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7583-2026 artfynd.xlsx
+++ b/artfynd/A 7583-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122923641</v>
       </c>
       <c r="B4" t="n">
-        <v>57082</v>
+        <v>57083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7583-2026 artfynd.xlsx
+++ b/artfynd/A 7583-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122923641</v>
       </c>
       <c r="B4" t="n">
-        <v>57083</v>
+        <v>57089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7583-2026 artfynd.xlsx
+++ b/artfynd/A 7583-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122923641</v>
       </c>
       <c r="B4" t="n">
-        <v>57089</v>
+        <v>57090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7583-2026 artfynd.xlsx
+++ b/artfynd/A 7583-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122923641</v>
       </c>
       <c r="B4" t="n">
-        <v>57090</v>
+        <v>57093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7583-2026 artfynd.xlsx
+++ b/artfynd/A 7583-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122923641</v>
       </c>
       <c r="B4" t="n">
-        <v>57093</v>
+        <v>57095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7583-2026 artfynd.xlsx
+++ b/artfynd/A 7583-2026 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>122904432</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -792,16 +787,11 @@
         <v>122923475</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -907,27 +897,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122923641</v>
+        <v>124778957</v>
       </c>
       <c r="B4" t="n">
-        <v>57095</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,33 +925,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väst Örkyttjärn, Vrm</t>
+          <t>V Örkyttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>373021</v>
+        <v>372941</v>
       </c>
       <c r="R4" t="n">
-        <v>6626086</v>
+        <v>6626051</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,17 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Satt I trädtoppar</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,32 +1006,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124778957</v>
+        <v>122923641</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1058,29 +1034,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>V Örkyttjärn, Vrm</t>
+          <t>Väst Örkyttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372941</v>
+        <v>373021</v>
       </c>
       <c r="R5" t="n">
-        <v>6626051</v>
+        <v>6626086</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1107,12 +1087,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Satt I trädtoppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
